--- a/source/guides/cdc/opioid-cds/ValueSet-office-visit.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-office-visit.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Expansion" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -27,6 +28,12 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/office-visit</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.114222.48.52</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -102,15 +109,27 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/731000124108/version/20250901</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>http://www.ama-assn.org/go/cpt|2023</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -129,9 +148,6 @@
     <t>http://snomed.info/sct</t>
   </si>
   <si>
-    <t>2020-09</t>
-  </si>
-  <si>
     <t>185463005</t>
   </si>
   <si>
@@ -163,9 +179,6 @@
   </si>
   <si>
     <t>http://www.ama-assn.org/go/cpt</t>
-  </si>
-  <si>
-    <t>2021</t>
   </si>
   <si>
     <t>99202</t>
@@ -347,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -455,15 +468,15 @@
         <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -472,6 +485,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -481,329 +502,353 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
